--- a/Tubex_Sep26.xlsx
+++ b/Tubex_Sep26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_8EEAD57358B5893C244D72FE58DD996BFF57AC91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_F711C2367A6A8797AE65830351ACC6C44D0365AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4508,8 +4508,8 @@
     <col min="13" max="13" width="14.7109375" style="99" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="99" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="99" customWidth="1"/>
-    <col min="16" max="181" width="8.7109375" style="99" customWidth="1"/>
-    <col min="182" max="16384" width="8.7109375" style="99"/>
+    <col min="16" max="182" width="8.7109375" style="99" customWidth="1"/>
+    <col min="183" max="16384" width="8.7109375" style="99"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -39642,14 +39642,14 @@
   </autoFilter>
   <mergeCells count="9">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Tubex_Sep26.xlsx
+++ b/Tubex_Sep26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F6075547E3CE5DE1E2F2D3749EDD3AEA0FBE3221" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_BC1D71211AA6DEC1A2F3D3749E13465A56EB5F50" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="16200" windowHeight="9270" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="16200" windowHeight="9270" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tubex_Dashboard" sheetId="1" r:id="rId1"/>
@@ -4578,8 +4578,8 @@
     <col min="13" max="13" width="14.7109375" style="99" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="99" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="99" hidden="1" customWidth="1"/>
-    <col min="16" max="188" width="8.7109375" style="99" customWidth="1"/>
-    <col min="189" max="16384" width="8.7109375" style="99"/>
+    <col min="16" max="190" width="8.7109375" style="99" customWidth="1"/>
+    <col min="191" max="16384" width="8.7109375" style="99"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">

--- a/Tubex_Sep26.xlsx
+++ b/Tubex_Sep26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3D5C4FC43C1DD4725D0A122BB0CD3D32C97801A0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_3D5C4F480125156A5D0A12ABB507872371680BAC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4455,8 +4455,8 @@
     <col min="13" max="13" width="14.7109375" style="99" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="99" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="99" hidden="1" customWidth="1"/>
-    <col min="16" max="194" width="8.7109375" style="99" customWidth="1"/>
-    <col min="195" max="16384" width="8.7109375" style="99"/>
+    <col min="16" max="195" width="8.7109375" style="99" customWidth="1"/>
+    <col min="196" max="16384" width="8.7109375" style="99"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -10233,15 +10233,15 @@
       </c>
       <c r="F19" s="158">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A19,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A19,TableInventory[Item ID],0)),0)</f>
-        <v>393</v>
+        <v>308</v>
       </c>
       <c r="G19" s="158">
         <f t="shared" si="1"/>
-        <v>247.8875908</v>
+        <v>162.8875908</v>
       </c>
       <c r="H19" s="165">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A19)*((TableBOM[Product ID]=$D$3)*($H$3&gt;0)+(TableBOM[Product ID]=$D$4)*($H$4&gt;0)+(TableBOM[Product ID]=$D$5)*($H$5&gt;0)+(TableBOM[Product ID]=$D$6)*($H$6&gt;0)+(TableBOM[Product ID]=$D$7)*($H$7&gt;0)+(TableBOM[Product ID]=$D$8)*($H$8&gt;0)))=0,"-",ROUND(F19/((SUMPRODUCT((TableBOM[Item ID]=A19)*TableBOM[Per 1000 Units]*((TableBOM[Product ID]=$D$3)*($H$3&gt;0)+(TableBOM[Product ID]=$D$4)*($H$4&gt;0)+(TableBOM[Product ID]=$D$5)*($H$5&gt;0)+(TableBOM[Product ID]=$D$6)*($H$6&gt;0)+(TableBOM[Product ID]=$D$7)*($H$7&gt;0)+(TableBOM[Product ID]=$D$8)*($H$8&gt;0)))/SUMPRODUCT((TableBOM[Item ID]=A19)*((TableBOM[Product ID]=$D$3)*($H$3&gt;0)+(TableBOM[Product ID]=$D$4)*($H$4&gt;0)+(TableBOM[Product ID]=$D$5)*($H$5&gt;0)+(TableBOM[Product ID]=$D$6)*($H$6&gt;0)+(TableBOM[Product ID]=$D$7)*($H$7&gt;0)+(TableBOM[Product ID]=$D$8)*($H$8&gt;0))))/1000),0)),"-")</f>
-        <v>66123</v>
+        <v>51821</v>
       </c>
       <c r="I19" s="160" t="str">
         <f t="shared" si="2"/>
@@ -10347,15 +10347,15 @@
       </c>
       <c r="F22" s="159">
         <f>IFERROR(INDEX(TableInventory[Store Balance],MATCH(A22,TableInventory[Item ID],0)),0)+IFERROR(INDEX(TableInventory[WIP],MATCH(A22,TableInventory[Item ID],0)),0)</f>
-        <v>875</v>
+        <v>930</v>
       </c>
       <c r="G22" s="158">
         <f t="shared" si="1"/>
-        <v>-5373.140800000001</v>
+        <v>-5318.140800000001</v>
       </c>
       <c r="H22" s="165">
         <f>IFERROR(IF(SUMPRODUCT((TableBOM[Item ID]=A22)*((TableBOM[Product ID]=$D$3)*($H$3&gt;0)+(TableBOM[Product ID]=$D$4)*($H$4&gt;0)+(TableBOM[Product ID]=$D$5)*($H$5&gt;0)+(TableBOM[Product ID]=$D$6)*($H$6&gt;0)+(TableBOM[Product ID]=$D$7)*($H$7&gt;0)+(TableBOM[Product ID]=$D$8)*($H$8&gt;0)))=0,"-",ROUND(F22/((SUMPRODUCT((TableBOM[Item ID]=A22)*TableBOM[Per 1000 Units]*((TableBOM[Product ID]=$D$3)*($H$3&gt;0)+(TableBOM[Product ID]=$D$4)*($H$4&gt;0)+(TableBOM[Product ID]=$D$5)*($H$5&gt;0)+(TableBOM[Product ID]=$D$6)*($H$6&gt;0)+(TableBOM[Product ID]=$D$7)*($H$7&gt;0)+(TableBOM[Product ID]=$D$8)*($H$8&gt;0)))/SUMPRODUCT((TableBOM[Item ID]=A22)*((TableBOM[Product ID]=$D$3)*($H$3&gt;0)+(TableBOM[Product ID]=$D$4)*($H$4&gt;0)+(TableBOM[Product ID]=$D$5)*($H$5&gt;0)+(TableBOM[Product ID]=$D$6)*($H$6&gt;0)+(TableBOM[Product ID]=$D$7)*($H$7&gt;0)+(TableBOM[Product ID]=$D$8)*($H$8&gt;0))))/1000),0)),"-")</f>
-        <v>109375</v>
+        <v>116250</v>
       </c>
       <c r="I22" s="160" t="str">
         <f t="shared" si="2"/>
@@ -30917,13 +30917,13 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="40.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" style="51" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" style="51" customWidth="1"/>
     <col min="7" max="7" width="11.140625" style="51" customWidth="1"/>
     <col min="8" max="8" width="8.85546875" style="52" customWidth="1"/>
-    <col min="9" max="9" width="7" style="51" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="7" style="51" customWidth="1"/>
     <col min="10" max="10" width="16.140625" style="136" customWidth="1"/>
     <col min="11" max="11" width="18" style="138" customWidth="1"/>
   </cols>
@@ -31138,11 +31138,11 @@
         <v>258</v>
       </c>
       <c r="I7" s="27">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="J7" s="219">
         <f>IFERROR(IF(H7+I7="","-",ROUND((H7+I7)/(IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units])&gt;0,AVERAGEIF(TableBOM[Item ID],A7,TableBOM[Per 1000 Units]),AVERAGEIF(TableBOM[Material Category],B7,TableBOM[Per 1000 Units])),AVERAGEIF(TableBOM[Material Category],B7,TableBOM[Per 1000 Units]))/1000),0)),"-")</f>
-        <v>66353</v>
+        <v>52002</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31171,10 +31171,12 @@
         <f t="shared" si="0"/>
         <v>875</v>
       </c>
-      <c r="I8" s="27"/>
+      <c r="I8" s="27">
+        <v>55</v>
+      </c>
       <c r="J8" s="219">
         <f>IFERROR(IF(H8+I8="","-",ROUND((H8+I8)/(IFERROR(IF(AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units])&gt;0,AVERAGEIF(TableBOM[Item ID],A8,TableBOM[Per 1000 Units]),AVERAGEIF(TableBOM[Material Category],B8,TableBOM[Per 1000 Units])),AVERAGEIF(TableBOM[Material Category],B8,TableBOM[Per 1000 Units]))/1000),0)),"-")</f>
-        <v>109375</v>
+        <v>116250</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
